--- a/Processed_Known_Motifs_With_Realignment.xlsx
+++ b/Processed_Known_Motifs_With_Realignment.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/enoch/Documents/Local Erill Research/drippy/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEABCF94-7A54-F247-A79A-DF86568792B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D569CCC0-0A82-344D-B7CA-CC7F27527659}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="47300" yWindow="500" windowWidth="16700" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12700" yWindow="1180" windowWidth="16700" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -483,7 +483,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -788,7 +788,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:G62"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
@@ -816,7 +815,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="2" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>25</v>
       </c>
@@ -836,7 +835,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
         <v>32</v>
       </c>
@@ -856,7 +855,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>23</v>
       </c>
@@ -876,7 +875,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>21</v>
       </c>
@@ -893,7 +892,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>39</v>
       </c>
@@ -910,7 +909,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="7" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>28</v>
       </c>
@@ -927,7 +926,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="8" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>34</v>
       </c>
@@ -947,7 +946,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="9" spans="1:7" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>18</v>
       </c>
@@ -965,7 +964,7 @@
       </c>
       <c r="F9"/>
     </row>
-    <row r="10" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
         <v>29</v>
       </c>
@@ -983,7 +982,7 @@
       </c>
       <c r="F10" s="2"/>
     </row>
-    <row r="11" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>13</v>
       </c>
@@ -1000,7 +999,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>27</v>
       </c>
@@ -1020,7 +1019,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>24</v>
       </c>
@@ -1040,7 +1039,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -1060,7 +1059,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:7" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>59</v>
       </c>
@@ -1078,7 +1077,7 @@
       </c>
       <c r="F15"/>
     </row>
-    <row r="16" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
         <v>47</v>
       </c>
@@ -1096,7 +1095,7 @@
       </c>
       <c r="F16" s="2"/>
     </row>
-    <row r="17" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
         <v>48</v>
       </c>
@@ -1116,7 +1115,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>35</v>
       </c>
@@ -1133,7 +1132,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="19" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>45</v>
       </c>
@@ -1153,7 +1152,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="20" spans="1:7" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>22</v>
       </c>
@@ -1174,7 +1173,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="21" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>40</v>
       </c>
@@ -1191,7 +1190,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="22" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>52</v>
       </c>
@@ -1208,7 +1207,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>41</v>
       </c>
@@ -1246,7 +1245,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="25" spans="1:7" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A25" s="1"/>
       <c r="B25" t="s">
         <v>5</v>
@@ -1262,7 +1261,7 @@
       </c>
       <c r="F25"/>
     </row>
-    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>1</v>
       </c>
@@ -1300,7 +1299,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <v>5</v>
       </c>
@@ -1320,7 +1319,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <v>53</v>
       </c>
@@ -1337,7 +1336,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <v>2</v>
       </c>
@@ -1354,7 +1353,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <v>17</v>
       </c>
@@ -1371,7 +1370,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
         <v>38</v>
       </c>
@@ -1388,7 +1387,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
         <v>11</v>
       </c>
@@ -1405,7 +1404,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
         <v>9</v>
       </c>
@@ -1425,7 +1424,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
         <v>10</v>
       </c>
@@ -1442,7 +1441,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="1">
         <v>19</v>
       </c>
@@ -1462,7 +1461,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="37" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="3">
         <v>0</v>
       </c>
@@ -1480,7 +1479,7 @@
       </c>
       <c r="F37" s="2"/>
     </row>
-    <row r="38" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="1">
         <v>4</v>
       </c>
@@ -1500,7 +1499,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="3">
         <v>54</v>
       </c>
@@ -1518,7 +1517,7 @@
       </c>
       <c r="F39" s="2"/>
     </row>
-    <row r="40" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="1">
         <v>55</v>
       </c>
@@ -1561,7 +1560,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="42" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="1">
         <v>56</v>
       </c>
@@ -1578,7 +1577,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="43" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="3">
         <v>49</v>
       </c>
@@ -1599,7 +1598,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="44" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="1">
         <v>50</v>
       </c>
@@ -1642,7 +1641,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="46" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="1">
         <v>46</v>
       </c>
@@ -1679,7 +1678,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="48" spans="1:7" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A48" s="3">
         <v>6</v>
       </c>
@@ -1699,7 +1698,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="49" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="1">
         <v>7</v>
       </c>
@@ -1719,7 +1718,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="50" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="1">
         <v>44</v>
       </c>
@@ -1736,7 +1735,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="51" spans="1:7" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A51" s="1">
         <v>20</v>
       </c>
@@ -1757,7 +1756,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="52" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="1">
         <v>16</v>
       </c>
@@ -1777,7 +1776,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="53" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" s="1">
         <v>31</v>
       </c>
@@ -1794,7 +1793,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="54" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A54" s="3">
         <v>26</v>
       </c>
@@ -1812,7 +1811,7 @@
       </c>
       <c r="F54" s="2"/>
     </row>
-    <row r="55" spans="1:7" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A55" s="1">
         <v>33</v>
       </c>
@@ -1832,7 +1831,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="56" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A56" s="1">
         <v>51</v>
       </c>
@@ -1849,7 +1848,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="57" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A57" s="1">
         <v>30</v>
       </c>
@@ -1869,7 +1868,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="58" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A58" s="1">
         <v>15</v>
       </c>
@@ -1889,7 +1888,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="59" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A59" s="1">
         <v>14</v>
       </c>
@@ -1909,7 +1908,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="60" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A60" s="1">
         <v>57</v>
       </c>
@@ -1926,7 +1925,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="61" spans="1:7" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A61" s="3">
         <v>58</v>
       </c>
@@ -1946,7 +1945,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="62" spans="1:7" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A62" s="1">
         <v>3</v>
       </c>
@@ -1965,22 +1964,7 @@
       <c r="F62"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G62" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="3">
-      <filters>
-        <filter val="P0A9E5"/>
-        <filter val="P0ACJ8"/>
-        <filter val="P0DN68"/>
-        <filter val="Q4UZF6"/>
-        <filter val="Q79VI7"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="6">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:G62" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
